--- a/slide_classification/TCGA_Results/Tissue_Type_Clustering/Conch1_5/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Tissue_Type_Clustering/Conch1_5/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -843,7 +843,7 @@
         <v>0.7939393939393939</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5943223443223442</v>
+        <v>0.5847069597069596</v>
       </c>
       <c r="D18" t="n">
         <v>0.6358695652173912</v>
@@ -852,7 +852,7 @@
         <v>0.7008426966292136</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6812435000270858</v>
+        <v>0.6788396538732396</v>
       </c>
     </row>
     <row r="19">
@@ -1430,10 +1430,10 @@
         <v>0.02355289135913477</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6812435000270858</v>
+        <v>0.6788396538732396</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07533023012261646</v>
+        <v>0.07816565211765233</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>

--- a/slide_classification/TCGA_Results/Tissue_Type_Clustering/Conch1_5/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Tissue_Type_Clustering/Conch1_5/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="baseline" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="baseline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -468,19 +468,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8640776699029126</v>
+        <v>0.883495145631068</v>
       </c>
       <c r="C2" t="n">
         <v>0.8556701030927835</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8392857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8811881188118812</v>
+        <v>0.8910891089108911</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8600554015233228</v>
+        <v>0.8718493036943999</v>
       </c>
     </row>
     <row r="3">
@@ -490,19 +490,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6992424242424242</v>
+        <v>0.7106060606060607</v>
       </c>
       <c r="C3" t="n">
         <v>0.5590659340659341</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6869565217391305</v>
+        <v>0.6978260869565217</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6802434456928839</v>
+        <v>0.6858614232209738</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6563770814350931</v>
+        <v>0.6633398762123726</v>
       </c>
     </row>
     <row r="4">
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7106741573033708</v>
+        <v>0.7358974358974359</v>
       </c>
       <c r="C4" t="n">
         <v>0.5713383838383839</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7021276595744681</v>
+        <v>0.7226006191950465</v>
       </c>
       <c r="E4" t="n">
-        <v>0.693939393939394</v>
+        <v>0.7077084977637464</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6695198986639042</v>
+        <v>0.6843862341736532</v>
       </c>
     </row>
     <row r="5">
@@ -534,19 +534,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8599869095669248</v>
+        <v>0.8758277321384118</v>
       </c>
       <c r="C5" t="n">
         <v>0.8268770175986671</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8320668693009118</v>
+        <v>0.8467934542237947</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8764476447644765</v>
+        <v>0.8842123359928732</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8488446103077449</v>
+        <v>0.8584276349884368</v>
       </c>
     </row>
     <row r="6">
@@ -556,19 +556,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8560606060606061</v>
+        <v>0.8515151515151516</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8342490842490842</v>
+        <v>0.8553113553113553</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7913043478260871</v>
+        <v>0.775</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7874531835205992</v>
+        <v>0.7818352059925093</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8172668054140942</v>
+        <v>0.815915428204754</v>
       </c>
     </row>
     <row r="7">
@@ -579,7 +579,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[[82, 6], [8, 7]]</t>
+          <t>[[84, 4], [8, 7]]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -589,17 +589,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[[85, 7], [11, 9]]</t>
+          <t>[[87, 5], [11, 9]]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>[[84, 5], [7, 5]]</t>
+          <t>[[85, 4], [7, 5]]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[[83, 5], [9, 6]]</t>
+          <t>[[84, 4], [9, 6]]</t>
         </is>
       </c>
     </row>
@@ -613,16 +613,16 @@
         <v>0.8349514563106796</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7731958762886598</v>
+        <v>0.7628865979381443</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7589285714285714</v>
+        <v>0.7321428571428571</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7821782178217822</v>
+        <v>0.7722772277227723</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7873135304624233</v>
+        <v>0.7755645347786133</v>
       </c>
     </row>
     <row r="9">
@@ -635,16 +635,16 @@
         <v>0.8204545454545455</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6414835164835164</v>
+        <v>0.7330586080586081</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7554347826086957</v>
+        <v>0.7195652173913043</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6961610486891385</v>
+        <v>0.6905430711610487</v>
       </c>
       <c r="F9" t="n">
-        <v>0.728383473308974</v>
+        <v>0.7409053605163767</v>
       </c>
     </row>
     <row r="10">
@@ -657,16 +657,16 @@
         <v>0.7411677753141168</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6077205882352942</v>
+        <v>0.6443487964291408</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6823195713835486</v>
+        <v>0.6510178645616951</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6281793842034806</v>
+        <v>0.6194922194922194</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6648468297841101</v>
+        <v>0.664006663949293</v>
       </c>
     </row>
     <row r="11">
@@ -679,16 +679,16 @@
         <v>0.8515904964874892</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7942086112795634</v>
+        <v>0.7946377947709131</v>
       </c>
       <c r="D11" t="n">
-        <v>0.782607716897033</v>
+        <v>0.7591845213365779</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8106087717205457</v>
+        <v>0.8033116825196034</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8097538990961579</v>
+        <v>0.8021811237786459</v>
       </c>
     </row>
     <row r="12">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.8681818181818182</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8186813186813187</v>
+        <v>0.7957875457875458</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8646739130434782</v>
+        <v>0.8157608695652173</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8258426966292134</v>
+        <v>0.8370786516853933</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8394206942097147</v>
+        <v>0.8292022213049937</v>
       </c>
     </row>
     <row r="13">
@@ -726,22 +726,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[[69, 15], [7, 6]]</t>
+          <t>[[65, 19], [4, 9]]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[[70, 22], [5, 15]]</t>
+          <t>[[68, 24], [6, 14]]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[[72, 17], [5, 7]]</t>
+          <t>[[71, 18], [5, 7]]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[71, 17], [5, 10]]</t>
+          <t>[[70, 19], [4, 10]]</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8640776699029126</v>
+        <v>0.8737864077669902</v>
       </c>
       <c r="C14" t="n">
-        <v>0.865979381443299</v>
+        <v>0.8556701030927835</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8303571428571429</v>
+        <v>0.8392857142857143</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8811881188118812</v>
+        <v>0.8910891089108911</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8604005782538089</v>
+        <v>0.8649578335140947</v>
       </c>
     </row>
     <row r="15">
@@ -774,19 +774,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5886363636363636</v>
+        <v>0.5943181818181819</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5</v>
+        <v>0.5590659340659341</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5836956521739131</v>
+        <v>0.6086956521739131</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5720973782771536</v>
+        <v>0.6137640449438202</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5611073485218575</v>
+        <v>0.5939609532504624</v>
       </c>
     </row>
     <row r="16">
@@ -796,19 +796,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6123655913978494</v>
+        <v>0.6231353785533352</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4640883977900552</v>
+        <v>0.5713383838383839</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5999247978943411</v>
+        <v>0.6326530612244898</v>
       </c>
       <c r="E16" t="n">
-        <v>0.592741935483871</v>
+        <v>0.6467408585055644</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5672801806415292</v>
+        <v>0.6184669205304433</v>
       </c>
     </row>
     <row r="17">
@@ -818,19 +818,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8337509134565194</v>
+        <v>0.8409630587032975</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8037819673064874</v>
+        <v>0.8268770175986671</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7951145489216556</v>
+        <v>0.8097667638483965</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8540402427339507</v>
+        <v>0.8707267547104471</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8216719181046532</v>
+        <v>0.837083398715202</v>
       </c>
     </row>
     <row r="18">
@@ -840,19 +840,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7939393939393939</v>
+        <v>0.8204545454545454</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5847069597069596</v>
+        <v>0.6167582417582418</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6358695652173912</v>
+        <v>0.645108695652174</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7008426966292136</v>
+        <v>0.6896067415730337</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6788396538732396</v>
+        <v>0.6929820561094987</v>
       </c>
     </row>
     <row r="19">
@@ -863,27 +863,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>[[87, 1], [12, 3]]</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[[81, 3], [11, 2]]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>[[89, 3], [15, 5]]</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>[[87, 2], [9, 3]]</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>[[86, 2], [12, 3]]</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>[[84, 0], [13, 0]]</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>[[89, 3], [16, 4]]</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>[[87, 2], [10, 2]]</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>[[86, 2], [13, 2]]</t>
         </is>
       </c>
     </row>
@@ -894,19 +894,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6116504854368932</v>
+        <v>0.6019417475728155</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3814432989690721</v>
+        <v>0.4123711340206185</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6785714285714286</v>
+        <v>0.6517857142857143</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7623762376237624</v>
+        <v>0.7425742574257426</v>
       </c>
       <c r="F20" t="n">
-        <v>0.608510362650289</v>
+        <v>0.6021682133262227</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6621212121212121</v>
+        <v>0.656439393939394</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4152930402930403</v>
+        <v>0.4331501831501832</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.5728260869565217</v>
       </c>
       <c r="E21" t="n">
-        <v>0.648876404494382</v>
+        <v>0.6376404494382022</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5837465772706369</v>
+        <v>0.5750140283710752</v>
       </c>
     </row>
     <row r="22">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5385304659498208</v>
+        <v>0.5312465312465313</v>
       </c>
       <c r="C22" t="n">
-        <v>0.337431693989071</v>
+        <v>0.3589565217391305</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.541128269776237</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5943775100401606</v>
+        <v>0.5786264441591784</v>
       </c>
       <c r="F22" t="n">
-        <v>0.510442060351906</v>
+        <v>0.5024894417302692</v>
       </c>
     </row>
     <row r="23">
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6687197689389985</v>
+        <v>0.6602653010420001</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4624246521322742</v>
+        <v>0.4944007171671896</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7091836734693876</v>
+        <v>0.6859889244068255</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7933913873315043</v>
+        <v>0.7790071048183124</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6584298704680412</v>
+        <v>0.6549155118585819</v>
       </c>
     </row>
     <row r="24">
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7560606060606061</v>
+        <v>0.7545454545454545</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4697802197802198</v>
+        <v>0.5192307692307692</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7233695652173913</v>
+        <v>0.7048913043478261</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7837078651685393</v>
+        <v>0.7621722846441947</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6832295640566891</v>
+        <v>0.685209953192061</v>
       </c>
     </row>
     <row r="25">
@@ -1005,27 +1005,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[[52, 36], [4, 11]]</t>
+          <t>[[51, 37], [4, 11]]</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[[31, 53], [7, 6]]</t>
+          <t>[[34, 50], [7, 6]]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[[66, 26], [10, 10]]</t>
+          <t>[[64, 28], [11, 9]]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[[71, 18], [6, 6]]</t>
+          <t>[[69, 20], [6, 6]]</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[[55, 33], [7, 8]]</t>
+          <t>[[54, 34], [7, 8]]</t>
         </is>
       </c>
     </row>
@@ -1036,19 +1036,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.912621359223301</v>
+        <v>0.8932038834951457</v>
       </c>
       <c r="C26" t="n">
-        <v>0.865979381443299</v>
+        <v>0.8865979381443299</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8660714285714286</v>
       </c>
       <c r="E26" t="n">
         <v>0.8712871287128713</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8767576816305821</v>
+        <v>0.8792900947309439</v>
       </c>
     </row>
     <row r="27">
@@ -1058,19 +1058,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7276515151515152</v>
+        <v>0.6609848484848485</v>
       </c>
       <c r="C27" t="n">
-        <v>0.565018315018315</v>
+        <v>0.6094322344322345</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6195652173913043</v>
+        <v>0.625</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6025280898876404</v>
+        <v>0.5664794007490637</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6286907843621937</v>
+        <v>0.6154741209165366</v>
       </c>
     </row>
     <row r="28">
@@ -1080,19 +1080,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7797576621525303</v>
+        <v>0.7083655083655084</v>
       </c>
       <c r="C28" t="n">
-        <v>0.5809238949817215</v>
+        <v>0.6453971419076105</v>
       </c>
       <c r="D28" t="n">
-        <v>0.651903651903652</v>
+        <v>0.6623115577889447</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6223756111590452</v>
+        <v>0.5825119236883943</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6587402050492371</v>
+        <v>0.6496465329376145</v>
       </c>
     </row>
     <row r="29">
@@ -1102,19 +1102,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9009957857296086</v>
+        <v>0.8729167447614049</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8339106392163717</v>
+        <v>0.8594628485676989</v>
       </c>
       <c r="D29" t="n">
-        <v>0.8237318237318237</v>
+        <v>0.830940416367552</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8561095971547111</v>
+        <v>0.8472225282941649</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8536869614581287</v>
+        <v>0.8526356344977052</v>
       </c>
     </row>
     <row r="30">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8916666666666667</v>
+        <v>0.9106060606060605</v>
       </c>
       <c r="C30" t="n">
-        <v>0.7522893772893773</v>
+        <v>0.7481684981684982</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7913043478260869</v>
+        <v>0.7679347826086957</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8492509363295879</v>
+        <v>0.8764044943820225</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8211278320279296</v>
+        <v>0.8257784589413193</v>
       </c>
     </row>
     <row r="31">
@@ -1147,27 +1147,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[[87, 1], [8, 7]]</t>
+          <t>[[87, 1], [10, 5]]</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[[82, 2], [11, 2]]</t>
+          <t>[[83, 1], [10, 3]]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[[91, 1], [15, 5]]</t>
+          <t>[[92, 0], [15, 5]]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>[[85, 4], [9, 3]]</t>
+          <t>[[86, 3], [10, 2]]</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[[86, 2], [11, 4]]</t>
+          <t>[[87, 1], [11, 4]]</t>
         </is>
       </c>
     </row>
@@ -1290,38 +1290,38 @@
         <v>413</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8600554015233228</v>
+        <v>0.8718493036943999</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01511109801758753</v>
+        <v>0.01568312661320368</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6563770814350931</v>
+        <v>0.6633398762123726</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05659417489566823</v>
+        <v>0.06083515843870103</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6695198986639042</v>
+        <v>0.6843862341736532</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05699311510767802</v>
+        <v>0.06602553969863248</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8488446103077449</v>
+        <v>0.8584276349884368</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0203109949702429</v>
+        <v>0.02290420161486076</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8172668054140942</v>
+        <v>0.815915428204754</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02896661016346237</v>
+        <v>0.03759957840049492</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[[83, 5], [9, 6]]</t>
+          <t>[[84, 4], [9, 6]]</t>
         </is>
       </c>
     </row>
@@ -1348,38 +1348,38 @@
         <v>413</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7873135304624233</v>
+        <v>0.7755645347786133</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02872610952497973</v>
+        <v>0.03736236411139434</v>
       </c>
       <c r="H3" t="n">
-        <v>0.728383473308974</v>
+        <v>0.7409053605163767</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06670596451126319</v>
+        <v>0.04842882985931222</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6648468297841101</v>
+        <v>0.664006663949293</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0518123838104779</v>
+        <v>0.04607199132159297</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8097538990961579</v>
+        <v>0.8021811237786459</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02612280071975975</v>
+        <v>0.03297034238762276</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8394206942097147</v>
+        <v>0.8292022213049937</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01826449882828232</v>
+        <v>0.02682656148645286</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[[71, 17], [5, 10]]</t>
+          <t>[[70, 19], [4, 10]]</t>
         </is>
       </c>
     </row>
@@ -1406,38 +1406,38 @@
         <v>413</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8604005782538089</v>
+        <v>0.8649578335140947</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01856996163775061</v>
+        <v>0.01940429668435084</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5611073485218575</v>
+        <v>0.5939609532504624</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03578745217407292</v>
+        <v>0.0213720832461325</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5672801806415292</v>
+        <v>0.6184669205304433</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05999002064169917</v>
+        <v>0.0284761111611934</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8216719181046532</v>
+        <v>0.837083398715202</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02355289135913477</v>
+        <v>0.02234555839640375</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6788396538732396</v>
+        <v>0.6929820561094987</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07816565211765233</v>
+        <v>0.07804254737605466</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>[[86, 2], [13, 2]]</t>
+          <t>[[86, 2], [12, 3]]</t>
         </is>
       </c>
     </row>
@@ -1464,38 +1464,38 @@
         <v>413</v>
       </c>
       <c r="F5" t="n">
-        <v>0.608510362650289</v>
+        <v>0.6021682133262227</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1415561480643666</v>
+        <v>0.1206220711777251</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5837465772706369</v>
+        <v>0.5750140283710752</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09922641815684428</v>
+        <v>0.08758181381157587</v>
       </c>
       <c r="J5" t="n">
-        <v>0.510442060351906</v>
+        <v>0.5024894417302692</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1018406348734496</v>
+        <v>0.08473262578584259</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6584298704680412</v>
+        <v>0.6549155118585819</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1217728286385972</v>
+        <v>0.1026619452009891</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6832295640566891</v>
+        <v>0.685209953192061</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1250720711619263</v>
+        <v>0.09831970466575789</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>[[55, 33], [7, 8]]</t>
+          <t>[[54, 34], [7, 8]]</t>
         </is>
       </c>
     </row>
@@ -1522,38 +1522,38 @@
         <v>413</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8767576816305821</v>
+        <v>0.8792900947309439</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02131339610615473</v>
+        <v>0.01102019388727503</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6286907843621937</v>
+        <v>0.6154741209165366</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06044661310903354</v>
+        <v>0.03390780032930492</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6587402050492371</v>
+        <v>0.6496465329376145</v>
       </c>
       <c r="K6" t="n">
-        <v>0.07427941367563111</v>
+        <v>0.04509277661931502</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8536869614581287</v>
+        <v>0.8526356344977052</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02971702885249396</v>
+        <v>0.01547512919147689</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8211278320279296</v>
+        <v>0.8257784589413193</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05337323591577132</v>
+        <v>0.06915185169514171</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>[[86, 2], [11, 4]]</t>
+          <t>[[87, 1], [11, 4]]</t>
         </is>
       </c>
     </row>
